--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CJ/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CJ/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\CJ\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21ABB80-562A-4F91-8AC9-26A9A4BFC80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA4A2FB-995C-4CE4-A776-09EACAF65270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,8 +180,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -501,34 +502,34 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>28.055555555555557</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2.4930458836085987</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>13.666666666666666</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>2.3048861143232218</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>37.444444444444443</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1.7579185924774154</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>26.388888888888893</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>1.5701203067847307</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>12.722222222222221</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1.8503002759312106</v>
       </c>
     </row>
@@ -536,34 +537,34 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>26.714285714285715</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>3.7733400639347709</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>12.571428571428571</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>2.8493942547579527</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>35.285714285714285</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>3.0118812346154309</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>24.857142857142858</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.7570718788090562</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>12.285714285714283</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>2.3838078115778791</v>
       </c>
     </row>
@@ -571,36 +572,46 @@
       <c r="A5" t="s">
         <v>28</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C6">
+      <c r="C6" s="1">
         <v>26.636363636363637</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>1.5666989036012804</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>13.636363636363637</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>2.3247678280949802</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>37.272727272727273</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2.7510328638861838</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>25.848484848484851</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>1.0735572888883258</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>12.212121212121211</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>2.1122538108892623</v>
       </c>
     </row>
@@ -608,39 +619,49 @@
       <c r="A7" t="s">
         <v>34</v>
       </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>23.833333333333332</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>2.1602468994692869</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>13.416666666666666</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1.9083151381956418</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>37.083333333333336</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>3.0235189211689524</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>24.777777777777775</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>1.4782371884055636</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>11.361111111111112</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>1.7333867513136263</v>
       </c>
     </row>
